--- a/backtest_runs/20260410_193731/by_symbol/GRR/GRR.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/GRR/GRR.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -538,10 +538,10 @@
         </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>100000</v>
@@ -630,10 +630,10 @@
         </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>100000</v>
@@ -679,7 +679,7 @@
         <v>-3535.699999999997</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="3" t="n">
         <v>96464.3</v>
@@ -771,7 +771,7 @@
         <v>-404.0800000000093</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K7" s="3" t="n">
         <v>100353.57</v>
@@ -860,10 +860,10 @@
         </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K9" s="2" t="n">
         <v>100808.16</v>
@@ -909,7 +909,7 @@
         <v>-151.5300000000057</v>
       </c>
       <c r="J10" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="3" t="n">
         <v>100656.63</v>
@@ -1139,7 +1139,7 @@
         <v>-50.51000000000789</v>
       </c>
       <c r="J15" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="3" t="n">
         <v>100959.69</v>
@@ -1185,7 +1185,7 @@
         <v>-606.119999999987</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="3" t="n">
         <v>100353.57</v>
@@ -1277,7 +1277,7 @@
         <v>-1111.220000000012</v>
       </c>
       <c r="J18" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="3" t="n">
         <v>99444.38999999998</v>
@@ -1369,7 +1369,7 @@
         <v>-454.5899999999993</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K20" s="3" t="n">
         <v>99949.48999999999</v>
@@ -1415,7 +1415,7 @@
         <v>-202.0399999999957</v>
       </c>
       <c r="J21" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="3" t="n">
         <v>99747.45</v>
@@ -1553,7 +1553,7 @@
         <v>-252.5499999999856</v>
       </c>
       <c r="J24" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K24" s="3" t="n">
         <v>100000</v>
@@ -1599,7 +1599,7 @@
         <v>-202.0400000000136</v>
       </c>
       <c r="J25" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K25" s="3" t="n">
         <v>99797.95999999999</v>
@@ -1645,7 +1645,7 @@
         <v>-202.0399999999957</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="3" t="n">
         <v>99595.91999999998</v>
